--- a/artfynd/A 6221-2024 artfynd.xlsx
+++ b/artfynd/A 6221-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6221-2024 artfynd.xlsx
+++ b/artfynd/A 6221-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>98323857</v>
       </c>
       <c r="B2" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549472.3542345765</v>
+        <v>549473</v>
       </c>
       <c r="R2" t="n">
-        <v>6225299.750934658</v>
+        <v>6225299</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -762,19 +757,9 @@
           <t>2020-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -807,6 +792,359 @@
           <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134035586</v>
+      </c>
+      <c r="B3" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åby 120, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>549454</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6225233</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramdala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134050884</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åby 120, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>549446</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6225267</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramdala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134192120</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åby 120, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549446</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6225278</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramdala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6221-2024 artfynd.xlsx
+++ b/artfynd/A 6221-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98323857</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134035586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134050884</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,8 +1165,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134192120</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>